--- a/attendance.xlsx
+++ b/attendance.xlsx
@@ -11,6 +11,7 @@
     <sheet name="Session_2026-03-19_002132" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Session_2026-03-19_114514" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="Session_2026-03-19_114558" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Session_2026-03-21_000140" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -2360,4 +2361,254 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="22" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Time</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Match Score</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Confirmed After (s)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN #1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>00:02:26</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN #2</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>00:02:26</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN #3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>00:02:26</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN #4</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>00:02:28</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN #5</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>00:02:28</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN #6</t>
+        </is>
+      </c>
+      <c r="B7" s="4" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>00:02:45</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN #7</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>00:02:45</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>